--- a/runac/demo/MPE_2026_T1_Chubut.xlsx
+++ b/runac/demo/MPE_2026_T1_Chubut.xlsx
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>90000555</t>
+          <t>90000588</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="O7" s="5" t="n">
-        <v>40310</v>
+        <v>40450</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1809,96 +1809,96 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC7" s="5" t="n">
+        <v>45704</v>
+      </c>
+      <c r="AD7" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="AE7" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="AF7" s="5" t="n">
+        <v>45680</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Juzgado</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Dato 4</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Dato 4</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB7" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="AC7" s="5" t="n">
-        <v>45809</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>46132</v>
-      </c>
-      <c r="AE7" s="5" t="n">
-        <v>46007</v>
-      </c>
-      <c r="AF7" s="5" t="n">
-        <v>46136</v>
-      </c>
-      <c r="AG7" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Dato 4</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>Dato 4</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1909,7 +1909,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45870</v>
+        <v>45773</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>90000696</t>
+          <t>90000765</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1973,14 +1973,14 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tailandia</t>
+          <t>Santa Lucía</t>
         </is>
       </c>
       <c r="O8" s="5" t="n">
-        <v>40628</v>
+        <v>41908</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1994,103 +1994,107 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="AB8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC8" s="5" t="n">
+        <v>45580</v>
+      </c>
+      <c r="AD8" s="5" t="n">
+        <v>45729</v>
+      </c>
+      <c r="AE8" s="5" t="n">
+        <v>46005</v>
+      </c>
+      <c r="AF8" s="5" t="n">
+        <v>45622</v>
+      </c>
+      <c r="AG8" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Dato 5</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Dato 5</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Autonomía</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="AC8" s="5" t="n">
-        <v>45712</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>46267</v>
-      </c>
-      <c r="AE8" s="5" t="n">
-        <v>45582</v>
-      </c>
-      <c r="AF8" s="5" t="n">
-        <v>46161</v>
-      </c>
-      <c r="AG8" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Juzgado</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Dato 5</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Dato 5</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45833</v>
+        <v>46009</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2099,12 +2103,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2114,7 +2118,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,12 +2128,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>90000855</t>
+          <t>90000902</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2149,19 +2153,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>San Bartolomé</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="O9" s="5" t="n">
-        <v>40910</v>
+        <v>42258</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -2175,32 +2179,32 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Publica</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2211,67 +2215,67 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC9" s="5" t="n">
+        <v>45907</v>
+      </c>
+      <c r="AD9" s="5" t="n">
+        <v>45964</v>
+      </c>
+      <c r="AE9" s="5" t="n">
+        <v>46033</v>
+      </c>
+      <c r="AF9" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="AG9" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Juzgado</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Dato 6</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Dato 6</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Reintegro familiar</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC9" s="5" t="n">
-        <v>45735</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>46278</v>
-      </c>
-      <c r="AE9" s="5" t="n">
-        <v>45665</v>
-      </c>
-      <c r="AF9" s="5" t="n">
-        <v>45947</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Encuentro espontáneo</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Dato 6</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>Dato 6</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Reintegro familiar</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46032</v>
+        <v>45733</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2280,12 +2284,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2295,7 +2299,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2305,12 +2309,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>90000967</t>
+          <t>90000980</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2330,23 +2334,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>San Cristóbal y Nieves</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>40694</v>
+        <v>42663</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2361,65 +2365,65 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AB10" s="6" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45959</v>
+        <v>45749</v>
       </c>
       <c r="AD10" s="5" t="n">
-        <v>45870</v>
+        <v>45816</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>45591</v>
+        <v>46155</v>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>45613</v>
+        <v>46025</v>
       </c>
       <c r="AG10" s="6" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -2444,19 +2448,19 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45932</v>
+        <v>45676</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2465,12 +2469,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2490,12 +2494,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2505,7 +2509,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>90001124</t>
+          <t>90001103</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2520,18 +2524,18 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Azerbayán</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
-        <v>40420</v>
+        <v>40307</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2546,27 +2550,27 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2577,30 +2581,30 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46143</v>
+        <v>45688</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>45694</v>
+        <v>45794</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>45688</v>
+        <v>46030</v>
       </c>
       <c r="AF11" s="5" t="n">
         <v>45794</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -2625,23 +2629,19 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 8</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45837</v>
+        <v>45845</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>90001239</t>
+          <t>90001319</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="O12" s="5" t="n">
@@ -2831,162 +2831,166 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Familia ampliada</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gaiman</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Díaz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Benjamín</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>90001397</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20-90001370-2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Turkmenistán</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>40419</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>No asiste</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Dato 10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC13" s="5" t="n">
+        <v>45601</v>
+      </c>
+      <c r="AD13" s="5" t="n">
+        <v>45780</v>
+      </c>
+      <c r="AE13" s="5" t="n">
+        <v>46120</v>
+      </c>
+      <c r="AF13" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="AG13" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>Dato 10</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Comodoro Rivadavia</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>Dato 10</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Romero</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Benjamín</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>90001431</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>20-90001370-2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Taiwán</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>41821</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Asiste</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB13" s="6" t="n">
-        <v>94</v>
-      </c>
-      <c r="AC13" s="5" t="n">
-        <v>45709</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>45601</v>
-      </c>
-      <c r="AE13" s="5" t="n">
-        <v>45780</v>
-      </c>
-      <c r="AF13" s="5" t="n">
-        <v>46120</v>
-      </c>
-      <c r="AG13" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2999,15 +3003,11 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 10</t>
-        </is>
-      </c>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46216</v>
+        <v>45957</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tucumán</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>90001568</t>
+          <t>90001574</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -3066,117 +3066,121 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>42259</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Asiste</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Dato 11</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>42354</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Asiste</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>45670</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>45644</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>46195</v>
+      </c>
+      <c r="AG14" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>Dato 11</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Dato 11</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Autonomía</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="AC14" s="5" t="n">
-        <v>46026</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>45686</v>
-      </c>
-      <c r="AE14" s="5" t="n">
-        <v>45670</v>
-      </c>
-      <c r="AF14" s="5" t="n">
-        <v>46238</v>
-      </c>
-      <c r="AG14" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Encuentro espontáneo</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Dato 11</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>Dato 11</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3192,7 +3196,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45955</v>
+        <v>45957</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3201,12 +3205,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Formosa</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3216,7 +3220,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3226,12 +3230,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>López</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3241,7 +3245,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>90001674</t>
+          <t>90001726</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3256,18 +3260,18 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Islandia</t>
+          <t>Islas Ultramarinas Menores de Estados Unidos</t>
         </is>
       </c>
       <c r="O15" s="5" t="n">
-        <v>40715</v>
+        <v>41474</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -3277,32 +3281,32 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Publica</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3313,67 +3317,67 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC15" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AD15" s="5" t="n">
+        <v>45921</v>
+      </c>
+      <c r="AE15" s="5" t="n">
+        <v>46208</v>
+      </c>
+      <c r="AF15" s="5" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AG15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Dato 12</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Dato 12</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AB15" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="AC15" s="5" t="n">
-        <v>46060</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>45760</v>
-      </c>
-      <c r="AE15" s="5" t="n">
-        <v>46007</v>
-      </c>
-      <c r="AF15" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AG15" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Encuentro espontáneo</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Adopción</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45722</v>
+        <v>45652</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3382,12 +3386,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3397,7 +3401,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3407,12 +3411,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3422,7 +3426,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>90001848</t>
+          <t>90001798</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3432,19 +3436,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Omán</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="O16" s="5" t="n">
-        <v>42450</v>
+        <v>40617</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -3458,107 +3462,107 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="AB16" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC16" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="AD16" s="5" t="n">
+        <v>46021</v>
+      </c>
+      <c r="AE16" s="5" t="n">
+        <v>46226</v>
+      </c>
+      <c r="AF16" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="AG16" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Policía</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Dato 13</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Dato 13</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Autonomía</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 13</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB16" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AC16" s="5" t="n">
-        <v>45927</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>46070</v>
-      </c>
-      <c r="AE16" s="5" t="n">
-        <v>45629</v>
-      </c>
-      <c r="AF16" s="5" t="n">
-        <v>46008</v>
-      </c>
-      <c r="AG16" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Policía</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45995</v>
+        <v>45626</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3567,12 +3571,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3582,7 +3586,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3592,12 +3596,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3607,7 +3611,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>90001999</t>
+          <t>90002008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3622,18 +3626,18 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Macedônia</t>
         </is>
       </c>
       <c r="O17" s="5" t="n">
-        <v>41988</v>
+        <v>40218</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -3653,7 +3657,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3663,7 +3667,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3673,73 +3677,77 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC17" s="5" t="n">
+        <v>46236</v>
+      </c>
+      <c r="AD17" s="5" t="n">
+        <v>45963</v>
+      </c>
+      <c r="AE17" s="5" t="n">
+        <v>45905</v>
+      </c>
+      <c r="AF17" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AG17" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Dato 14</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Dato 14</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AB17" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="AC17" s="5" t="n">
-        <v>46127</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>45838</v>
-      </c>
-      <c r="AE17" s="5" t="n">
-        <v>46148</v>
-      </c>
-      <c r="AF17" s="5" t="n">
-        <v>46236</v>
-      </c>
-      <c r="AG17" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Reintegro familiar</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 14</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45596</v>
+        <v>45862</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3748,12 +3756,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3763,7 +3771,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3773,12 +3781,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>López</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3788,7 +3796,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>90002107</t>
+          <t>90002077</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3798,23 +3806,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Rusia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="O18" s="5" t="n">
-        <v>40812</v>
+        <v>40913</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3824,103 +3832,111 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC18" s="5" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AD18" s="5" t="n">
+        <v>45797</v>
+      </c>
+      <c r="AE18" s="5" t="n">
+        <v>46051</v>
+      </c>
+      <c r="AF18" s="5" t="n">
+        <v>46074</v>
+      </c>
+      <c r="AG18" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Dato 15</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Dato 15</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Autonomía</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB18" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AC18" s="5" t="n">
-        <v>46024</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>46005</v>
-      </c>
-      <c r="AE18" s="5" t="n">
-        <v>46115</v>
-      </c>
-      <c r="AF18" s="5" t="n">
-        <v>46168</v>
-      </c>
-      <c r="AG18" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Encuentro espontáneo</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 15</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45966</v>
+        <v>46081</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3929,12 +3945,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Entre Ríos</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3944,7 +3960,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3954,12 +3970,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Villalba</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3969,7 +3985,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>90002243</t>
+          <t>90002227</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3984,112 +4000,116 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Gabón</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="O19" s="5" t="n">
-        <v>40463</v>
+        <v>42265</v>
       </c>
       <c r="P19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>No asiste</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Dato 16</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC19" s="5" t="n">
+        <v>45957</v>
+      </c>
+      <c r="AD19" s="5" t="n">
+        <v>45832</v>
+      </c>
+      <c r="AE19" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="AF19" s="5" t="n">
+        <v>45755</v>
+      </c>
+      <c r="AG19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>No asiste</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Policía</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>Dato 16</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Dato 16</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AC19" s="5" t="n">
-        <v>46007</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>46239</v>
-      </c>
-      <c r="AE19" s="5" t="n">
-        <v>46167</v>
-      </c>
-      <c r="AF19" s="5" t="n">
-        <v>45668</v>
-      </c>
-      <c r="AG19" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Dato 16</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>Dato 16</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -4101,7 +4121,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45884</v>
+        <v>46277</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4110,12 +4130,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4125,7 +4145,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4135,12 +4155,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4150,7 +4170,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>90002384</t>
+          <t>90002371</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4160,23 +4180,23 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Lesoto</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="O20" s="5" t="n">
-        <v>42384</v>
+        <v>40689</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4186,107 +4206,103 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC20" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AD20" s="5" t="n">
+        <v>45848</v>
+      </c>
+      <c r="AE20" s="5" t="n">
+        <v>45598</v>
+      </c>
+      <c r="AF20" s="5" t="n">
+        <v>45890</v>
+      </c>
+      <c r="AG20" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 17</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Dato 17</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Dato 17</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AB20" s="6" t="n">
-        <v>93</v>
-      </c>
-      <c r="AC20" s="5" t="n">
-        <v>45971</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>45759</v>
-      </c>
-      <c r="AE20" s="5" t="n">
-        <v>45962</v>
-      </c>
-      <c r="AF20" s="5" t="n">
-        <v>45596</v>
-      </c>
-      <c r="AG20" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4295,12 +4311,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4310,7 +4326,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4320,12 +4336,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4335,7 +4351,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>90002488</t>
+          <t>90002540</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4350,18 +4366,18 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Malasia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="O21" s="5" t="n">
-        <v>41411</v>
+        <v>41498</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -4376,98 +4392,102 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB21" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC21" s="5" t="n">
+        <v>45751</v>
+      </c>
+      <c r="AD21" s="5" t="n">
+        <v>45599</v>
+      </c>
+      <c r="AE21" s="5" t="n">
+        <v>45630</v>
+      </c>
+      <c r="AF21" s="5" t="n">
+        <v>45644</v>
+      </c>
+      <c r="AG21" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Dato 18</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Dato 18</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB21" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC21" s="5" t="n">
-        <v>45755</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>45794</v>
-      </c>
-      <c r="AE21" s="5" t="n">
-        <v>46105</v>
-      </c>
-      <c r="AF21" s="5" t="n">
-        <v>45604</v>
-      </c>
-      <c r="AG21" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46048</v>
+        <v>46128</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4476,12 +4496,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4491,7 +4511,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4501,12 +4521,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4516,7 +4536,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>90002663</t>
+          <t>90002612</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4526,19 +4546,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Svalbard y Jan Mayen</t>
+          <t>Islas de Åland</t>
         </is>
       </c>
       <c r="O22" s="5" t="n">
-        <v>40477</v>
+        <v>42536</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4552,32 +4572,32 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -4592,43 +4612,43 @@
         </is>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46273</v>
+        <v>45748</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>46169</v>
+        <v>45803</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>45843</v>
+        <v>46227</v>
       </c>
       <c r="AF22" s="5" t="n">
-        <v>46054</v>
+        <v>45708</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Dato 19</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Dato 19</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Dato 19</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Dato 19</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
       <c r="AL22" t="inlineStr">
         <is>
           <t>No</t>
@@ -4636,19 +4656,23 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 19</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45811</v>
+        <v>45706</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4657,7 +4681,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4672,7 +4696,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4682,12 +4706,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4697,7 +4721,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>90002816</t>
+          <t>90002804</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4712,18 +4736,18 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Yibuti</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="O23" s="5" t="n">
-        <v>41991</v>
+        <v>42423</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4743,93 +4767,101 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="AC23" s="5" t="n">
+        <v>46034</v>
+      </c>
+      <c r="AD23" s="5" t="n">
+        <v>45997</v>
+      </c>
+      <c r="AE23" s="5" t="n">
+        <v>45828</v>
+      </c>
+      <c r="AF23" s="5" t="n">
+        <v>46199</v>
+      </c>
+      <c r="AG23" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Dato 20</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Dato 20</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AB23" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC23" s="5" t="n">
-        <v>45745</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>45782</v>
-      </c>
-      <c r="AE23" s="5" t="n">
-        <v>45637</v>
-      </c>
-      <c r="AF23" s="5" t="n">
-        <v>46034</v>
-      </c>
-      <c r="AG23" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Policía</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Reintegro familiar</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45935</v>
+        <v>46196</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4838,12 +4870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4853,7 +4885,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4863,12 +4895,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4878,7 +4910,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>90002906</t>
+          <t>90002896</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4888,23 +4920,23 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="O24" s="5" t="n">
-        <v>40804</v>
+        <v>40442</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -4914,66 +4946,66 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB24" s="6" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45680</v>
+        <v>46258</v>
       </c>
       <c r="AD24" s="5" t="n">
-        <v>46258</v>
+        <v>45689</v>
       </c>
       <c r="AE24" s="5" t="n">
-        <v>45689</v>
+        <v>45889</v>
       </c>
       <c r="AF24" s="5" t="n">
-        <v>45889</v>
+        <v>45790</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -5003,7 +5035,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -5023,12 +5055,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5038,7 +5070,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5048,12 +5080,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5063,7 +5095,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>90003069</t>
+          <t>90003076</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5073,19 +5105,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Anguila</t>
+          <t>Isla de Navidad</t>
         </is>
       </c>
       <c r="O25" s="5" t="n">
-        <v>41771</v>
+        <v>41555</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -5208,7 +5240,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5393,7 +5425,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5582,7 +5614,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5763,7 +5795,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Entre Ríos</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5948,7 +5980,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5963,7 +5995,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5973,12 +6005,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5988,7 +6020,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>90003756</t>
+          <t>90003710</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -5998,23 +6030,23 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Belice</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O30" s="5" t="n">
-        <v>41384</v>
+        <v>41835</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -6024,51 +6056,47 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 27</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AB30" s="6" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="AC30" s="5" t="n">
         <v>45715</v>
@@ -6133,7 +6161,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6314,7 +6342,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6499,12 +6527,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6514,7 +6542,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6529,7 +6557,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -6539,7 +6567,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>90004117</t>
+          <t>90004188</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -6554,14 +6582,14 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Zimbabue</t>
+          <t>Bhután</t>
         </is>
       </c>
       <c r="O33" s="5" t="n">
-        <v>40585</v>
+        <v>41030</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -6575,99 +6603,103 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="5" t="n">
+        <v>45860</v>
+      </c>
+      <c r="AD33" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="AE33" s="5" t="n">
+        <v>45670</v>
+      </c>
+      <c r="AF33" s="5" t="n">
+        <v>45797</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Encuentro espontáneo</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Dato 30</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Dato 30</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Adopción</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AB33" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC33" s="5" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>46276</v>
-      </c>
-      <c r="AE33" s="5" t="n">
-        <v>45860</v>
-      </c>
-      <c r="AF33" s="5" t="n">
-        <v>45817</v>
-      </c>
-      <c r="AG33" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Juzgado</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
